--- a/Docs/Status Report.xlsx
+++ b/Docs/Status Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d0d25a1f11c8555b/Desktop/SpaceLandMapper Docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_EB5928CFD27D524EED0CB85448604E780A81975A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_EB5928CFD27D524EED0CB85448604E780A81975A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADA6364F-CD36-48A1-8F68-031BB1B54A3C}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
